--- a/results_0305/all_resultsVip.xlsx
+++ b/results_0305/all_resultsVip.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LuanVanThs\code\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\vrptw-for-pisso\results_0305\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2499E2CE-2785-48A3-93EB-FE34C02E149C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DCCB83-E98D-4489-A455-EE09B030E163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -412,7 +399,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,16 +415,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -445,17 +457,104 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -776,7 +875,7 @@
     <col min="17" max="17" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -804,11 +903,11 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
       <c r="P1" t="s">
         <v>122</v>
       </c>
@@ -816,7 +915,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -861,8 +960,22 @@
         <f>C2-N2</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S2" s="3">
+        <v>10</v>
+      </c>
+      <c r="T2" s="4">
+        <v>828.94</v>
+      </c>
+      <c r="U2">
+        <f>B2-S2</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f>C2-T2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -904,11 +1017,25 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>C3-N3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q3:Q34" si="1">C3-N3</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="3">
+        <v>10</v>
+      </c>
+      <c r="T3" s="4">
+        <v>828.94</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U57" si="2">B3-S3</f>
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V57" si="3">C3-T3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -950,11 +1077,25 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>C4-N4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S4" s="3">
+        <v>10</v>
+      </c>
+      <c r="T4" s="4">
+        <v>828.06</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -996,11 +1137,25 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>C5-N5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="3">
+        <v>10</v>
+      </c>
+      <c r="T5" s="4">
+        <v>824.78</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -1042,11 +1197,25 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>C6-N6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="3">
+        <v>10</v>
+      </c>
+      <c r="T6" s="4">
+        <v>828.94</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -1088,11 +1257,25 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>C7-N7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="3">
+        <v>10</v>
+      </c>
+      <c r="T7" s="4">
+        <v>828.94</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1134,11 +1317,25 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>C8-N8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>10</v>
+      </c>
+      <c r="T8" s="4">
+        <v>828.94</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -1180,11 +1377,25 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <f>C9-N9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="3">
+        <v>10</v>
+      </c>
+      <c r="T9" s="4">
+        <v>828.94</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -1226,11 +1437,25 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <f>C10-N10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
+        <v>10</v>
+      </c>
+      <c r="T10" s="4">
+        <v>828.94</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1272,11 +1497,25 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <f>C11-N11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="3">
+        <v>3</v>
+      </c>
+      <c r="T11" s="4">
+        <v>591.55999999999995</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -1318,11 +1557,25 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>C12-N12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>3</v>
+      </c>
+      <c r="T12" s="4">
+        <v>591.55999999999995</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1364,11 +1617,25 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <f>C13-N13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>3</v>
+      </c>
+      <c r="T13" s="4">
+        <v>591.16999999999996</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1410,11 +1677,25 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <f>C14-N14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>3</v>
+      </c>
+      <c r="T14" s="4">
+        <v>590.6</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -1456,11 +1737,25 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <f>C15-N15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>3</v>
+      </c>
+      <c r="T15" s="4">
+        <v>588.88</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1502,11 +1797,25 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <f>C16-N16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="3">
+        <v>3</v>
+      </c>
+      <c r="T16" s="4">
+        <v>588.49</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -1548,11 +1857,25 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>C17-N17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
+        <v>3</v>
+      </c>
+      <c r="T17" s="4">
+        <v>588.29</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1594,11 +1917,25 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <f>C18-N18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
+        <v>3</v>
+      </c>
+      <c r="T18" s="4">
+        <v>588.32000000000005</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -1639,12 +1976,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q19" s="2">
-        <f>C19-N19</f>
+      <c r="Q19" s="1">
+        <f t="shared" si="1"/>
         <v>-4.2000000000000455</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S19" s="3">
+        <v>20</v>
+      </c>
+      <c r="T19" s="4">
+        <v>1637.7</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="3"/>
+        <v>8.8999999999998636</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1685,12 +2036,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q20" s="2">
-        <f>C20-N20</f>
+      <c r="Q20" s="1">
+        <f t="shared" si="1"/>
         <v>-13.309999999999945</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S20" s="3">
+        <v>18</v>
+      </c>
+      <c r="T20" s="4">
+        <v>1466.6</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="3"/>
+        <v>6.2100000000000364</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1731,12 +2096,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q21" s="2">
-        <f>C21-N21</f>
+      <c r="Q21" s="1">
+        <f t="shared" si="1"/>
         <v>-35.029999999999973</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S21" s="3">
+        <v>14</v>
+      </c>
+      <c r="T21" s="4">
+        <v>1208.7</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="3"/>
+        <v>48.950000000000045</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -1778,11 +2157,25 @@
         <v>3</v>
       </c>
       <c r="Q22">
-        <f>C22-N22</f>
+        <f t="shared" si="1"/>
         <v>10.190000000000055</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S22" s="3">
+        <v>11</v>
+      </c>
+      <c r="T22" s="4">
+        <v>976.61</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="3"/>
+        <v>40.889999999999986</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1824,11 +2217,25 @@
         <v>2</v>
       </c>
       <c r="Q23">
-        <f>C23-N23</f>
+        <f t="shared" si="1"/>
         <v>16.7800000000002</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S23" s="3">
+        <v>15</v>
+      </c>
+      <c r="T23" s="4">
+        <v>1355.3</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="3"/>
+        <v>38.590000000000146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1870,11 +2277,25 @@
         <v>1</v>
       </c>
       <c r="Q24">
-        <f>C24-N24</f>
+        <f t="shared" si="1"/>
         <v>0.96000000000003638</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S24" s="3">
+        <v>13</v>
+      </c>
+      <c r="T24" s="4">
+        <v>1234.5999999999999</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="3"/>
+        <v>18.3900000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -1915,12 +2336,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q25" s="2">
-        <f>C25-N25</f>
+      <c r="Q25" s="1">
+        <f t="shared" si="1"/>
         <v>-10.820000000000164</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S25" s="3">
+        <v>11</v>
+      </c>
+      <c r="T25" s="4">
+        <v>1064.5999999999999</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="3"/>
+        <v>29.240000000000009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1961,12 +2396,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q26" s="2">
-        <f>C26-N26</f>
+      <c r="Q26" s="1">
+        <f t="shared" si="1"/>
         <v>-2.7799999999999727</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S26" s="3">
+        <v>10</v>
+      </c>
+      <c r="T26" s="4">
+        <v>938.2</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="3"/>
+        <v>19.899999999999977</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -2007,12 +2456,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q27" s="2">
-        <f>C27-N27</f>
+      <c r="Q27" s="1">
+        <f t="shared" si="1"/>
         <v>-40.690000000000055</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S27" s="3">
+        <v>13</v>
+      </c>
+      <c r="T27" s="4">
+        <v>1146.9000000000001</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="3"/>
+        <v>7.1399999999998727</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -2054,11 +2517,25 @@
         <v>3</v>
       </c>
       <c r="Q28">
-        <f>C28-N28</f>
+        <f t="shared" si="1"/>
         <v>16.259999999999991</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S28" s="3">
+        <v>12</v>
+      </c>
+      <c r="T28" s="4">
+        <v>1068</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="3"/>
+        <v>67.099999999999909</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2099,12 +2576,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q29" s="2">
-        <f>C29-N29</f>
+      <c r="Q29" s="1">
+        <f t="shared" si="1"/>
         <v>-25.079999999999927</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S29" s="3">
+        <v>12</v>
+      </c>
+      <c r="T29" s="4">
+        <v>1048.7</v>
+      </c>
+      <c r="U29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <f t="shared" si="3"/>
+        <v>22.940000000000055</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -2146,11 +2637,25 @@
         <v>2</v>
       </c>
       <c r="Q30">
-        <f>C30-N30</f>
+        <f t="shared" si="1"/>
         <v>11.539999999999964</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S30" s="3">
+        <v>10</v>
+      </c>
+      <c r="T30" s="4">
+        <v>953.63</v>
+      </c>
+      <c r="U30">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="3"/>
+        <v>40.049999999999955</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -2191,12 +2696,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q31" s="2">
-        <f>C31-N31</f>
+      <c r="Q31" s="1">
+        <f t="shared" si="1"/>
         <v>-62.629999999999882</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S31" s="3">
+        <v>8</v>
+      </c>
+      <c r="T31" s="4">
+        <v>1143.2</v>
+      </c>
+      <c r="U31">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="3"/>
+        <v>46.539999999999964</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -2237,12 +2756,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q32" s="2">
-        <f>C32-N32</f>
+      <c r="Q32" s="1">
+        <f t="shared" si="1"/>
         <v>-44.230000000000018</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S32" s="3">
+        <v>8</v>
+      </c>
+      <c r="T32" s="4">
+        <v>1034.4000000000001</v>
+      </c>
+      <c r="U32">
+        <f t="shared" si="2"/>
+        <v>-4</v>
+      </c>
+      <c r="V32">
+        <f t="shared" si="3"/>
+        <v>113.06999999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -2283,12 +2816,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q33" s="2">
-        <f>C33-N33</f>
+      <c r="Q33" s="1">
+        <f t="shared" si="1"/>
         <v>-28.740000000000009</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S33" s="3">
+        <v>6</v>
+      </c>
+      <c r="T33" s="4">
+        <v>874.87</v>
+      </c>
+      <c r="U33">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="3"/>
+        <v>35.889999999999986</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -2329,12 +2876,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q34" s="2">
-        <f>C34-N34</f>
+      <c r="Q34" s="1">
+        <f t="shared" si="1"/>
         <v>-50.669999999999959</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S34" s="3">
+        <v>5</v>
+      </c>
+      <c r="T34" s="4">
+        <v>735.8</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="V34">
+        <f t="shared" si="3"/>
+        <v>39.050000000000068</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -2376,11 +2937,25 @@
         <v>1</v>
       </c>
       <c r="Q35">
-        <f>C35-N35</f>
+        <f t="shared" ref="Q35:Q57" si="4">C35-N35</f>
         <v>3.8000000000000682</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S35" s="3">
+        <v>5</v>
+      </c>
+      <c r="T35" s="4">
+        <v>954.16</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="V35">
+        <f t="shared" si="3"/>
+        <v>44.07000000000005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -2422,11 +2997,25 @@
         <v>1</v>
       </c>
       <c r="Q36">
-        <f>C36-N36</f>
+        <f t="shared" si="4"/>
         <v>44.82000000000005</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S36" s="3">
+        <v>4</v>
+      </c>
+      <c r="T36" s="4">
+        <v>879.86</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <f t="shared" si="3"/>
+        <v>71.100000000000023</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>29</v>
       </c>
@@ -2467,12 +3056,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q37" s="2">
-        <f>C37-N37</f>
+      <c r="Q37" s="1">
+        <f t="shared" si="4"/>
         <v>-38.720000000000027</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S37" s="3">
+        <v>4</v>
+      </c>
+      <c r="T37" s="4">
+        <v>797.99</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <f t="shared" si="3"/>
+        <v>53.899999999999977</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -2514,11 +3117,25 @@
         <v>1</v>
       </c>
       <c r="Q38">
-        <f>C38-N38</f>
+        <f t="shared" si="4"/>
         <v>10.739999999999895</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S38" s="3">
+        <v>4</v>
+      </c>
+      <c r="T38" s="4">
+        <v>705.33</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="3"/>
+        <v>32.229999999999905</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -2559,12 +3176,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q39" s="2">
-        <f>C39-N39</f>
+      <c r="Q39" s="1">
+        <f t="shared" si="4"/>
         <v>-4.8199999999999363</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S39" s="3">
+        <v>5</v>
+      </c>
+      <c r="T39" s="4">
+        <v>859.39</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="3"/>
+        <v>44.950000000000045</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>32</v>
       </c>
@@ -2605,12 +3236,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q40" s="3">
-        <f>C40-N40</f>
+      <c r="Q40">
+        <f t="shared" si="4"/>
         <v>25.299999999999955</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S40" s="3">
+        <v>6</v>
+      </c>
+      <c r="T40" s="4">
+        <v>905.21</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="3"/>
+        <v>59.459999999999923</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -2651,12 +3296,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q41" s="2">
-        <f>C41-N41</f>
+      <c r="Q41" s="1">
+        <f t="shared" si="4"/>
         <v>-112.25999999999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S41" s="3">
+        <v>4</v>
+      </c>
+      <c r="T41" s="4">
+        <v>753.15</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <f t="shared" si="3"/>
+        <v>20.300000000000068</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -2697,12 +3356,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q42" s="2">
-        <f>C42-N42</f>
+      <c r="Q42" s="1">
+        <f t="shared" si="4"/>
         <v>-27.700000000000045</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S42" s="3">
+        <v>14</v>
+      </c>
+      <c r="T42" s="4">
+        <v>1619.8</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="3"/>
+        <v>49.450000000000045</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2743,12 +3416,26 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q43" s="2">
-        <f>C43-N43</f>
+      <c r="Q43" s="1">
+        <f t="shared" si="4"/>
         <v>-61.6400000000001</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S43" s="3">
+        <v>14</v>
+      </c>
+      <c r="T43" s="4">
+        <v>1457.4</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="3"/>
+        <v>35.709999999999809</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -2790,11 +3477,25 @@
         <v>1</v>
       </c>
       <c r="Q44">
-        <f>C44-N44</f>
+        <f t="shared" si="4"/>
         <v>80.819999999999936</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S44" s="3">
+        <v>11</v>
+      </c>
+      <c r="T44" s="4">
+        <v>1258</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V44">
+        <f t="shared" si="3"/>
+        <v>84.490000000000009</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -2836,11 +3537,25 @@
         <v>1</v>
       </c>
       <c r="Q45">
-        <f>C45-N45</f>
+        <f t="shared" si="4"/>
         <v>15.670000000000073</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S45" s="3">
+        <v>10</v>
+      </c>
+      <c r="T45" s="4">
+        <v>1135.5</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V45">
+        <f t="shared" si="3"/>
+        <v>15.650000000000091</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -2881,12 +3596,26 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q46" s="2">
-        <f>C46-N46</f>
+      <c r="Q46" s="1">
+        <f t="shared" si="4"/>
         <v>-48.25</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S46" s="3">
+        <v>15</v>
+      </c>
+      <c r="T46" s="4">
+        <v>1513.7</v>
+      </c>
+      <c r="U46">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V46">
+        <f t="shared" si="3"/>
+        <v>67.490000000000009</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -2928,11 +3657,25 @@
         <v>3</v>
       </c>
       <c r="Q47">
-        <f>C47-N47</f>
+        <f t="shared" si="4"/>
         <v>4.4800000000000182</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S47" s="3">
+        <v>13</v>
+      </c>
+      <c r="T47" s="4">
+        <v>1378</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V47">
+        <f t="shared" si="3"/>
+        <v>51.210000000000036</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>40</v>
       </c>
@@ -2974,11 +3717,25 @@
         <v>1</v>
       </c>
       <c r="Q48">
-        <f>C48-N48</f>
+        <f t="shared" si="4"/>
         <v>38.619999999999891</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S48" s="3">
+        <v>12</v>
+      </c>
+      <c r="T48" s="4">
+        <v>1212.8</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <f t="shared" si="3"/>
+        <v>56.299999999999955</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>41</v>
       </c>
@@ -3020,57 +3777,85 @@
         <v>1</v>
       </c>
       <c r="Q49">
-        <f>C49-N49</f>
+        <f t="shared" si="4"/>
         <v>19.029999999999973</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="S49" s="3">
+        <v>11</v>
+      </c>
+      <c r="T49" s="4">
+        <v>1117.5</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <f t="shared" si="3"/>
+        <v>41.349999999999909</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="1">
         <v>6</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="1">
         <v>1338.49</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>2572.4699999999998</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="1">
         <v>163</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>896.84</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="1">
         <v>400</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="1">
         <v>96</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="1">
         <v>621.1</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="L50" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M50" s="2">
+      <c r="M50" s="1">
         <v>4</v>
       </c>
-      <c r="N50" s="2">
+      <c r="N50" s="1">
         <v>1406.94</v>
       </c>
-      <c r="P50" s="2">
+      <c r="P50" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q50" s="2">
-        <f>C50-N50</f>
+      <c r="Q50" s="1">
+        <f t="shared" si="4"/>
         <v>-68.450000000000045</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S50" s="3">
+        <v>9</v>
+      </c>
+      <c r="T50" s="4">
+        <v>1261.8</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="2"/>
+        <v>-3</v>
+      </c>
+      <c r="V50">
+        <f t="shared" si="3"/>
+        <v>76.690000000000055</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>43</v>
       </c>
@@ -3111,12 +3896,26 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Q51" s="2">
-        <f>C51-N51</f>
+      <c r="Q51" s="1">
+        <f t="shared" si="4"/>
         <v>-194.75</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S51" s="3">
+        <v>8</v>
+      </c>
+      <c r="T51" s="4">
+        <v>1095.5999999999999</v>
+      </c>
+      <c r="U51">
+        <f t="shared" si="2"/>
+        <v>-2</v>
+      </c>
+      <c r="V51">
+        <f t="shared" si="3"/>
+        <v>75.300000000000182</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>44</v>
       </c>
@@ -3157,12 +3956,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q52" s="2">
-        <f>C52-N52</f>
+      <c r="Q52" s="1">
+        <f t="shared" si="4"/>
         <v>-83.949999999999932</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S52" s="3">
+        <v>5</v>
+      </c>
+      <c r="T52" s="4">
+        <v>926.82</v>
+      </c>
+      <c r="U52">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <f t="shared" si="3"/>
+        <v>38.849999999999909</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -3203,12 +4016,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q53" s="3">
-        <f>C53-N53</f>
+      <c r="Q53">
+        <f t="shared" si="4"/>
         <v>7.1699999999999591</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S53" s="3">
+        <v>4</v>
+      </c>
+      <c r="T53" s="4">
+        <v>786.38</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="3"/>
+        <v>19.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>46</v>
       </c>
@@ -3249,12 +4076,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q54" s="2">
-        <f>C54-N54</f>
+      <c r="Q54" s="1">
+        <f t="shared" si="4"/>
         <v>-25.690000000000055</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S54" s="3">
+        <v>7</v>
+      </c>
+      <c r="T54" s="4">
+        <v>1157.5999999999999</v>
+      </c>
+      <c r="U54">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="V54">
+        <f t="shared" si="3"/>
+        <v>114.36000000000013</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>47</v>
       </c>
@@ -3295,12 +4136,26 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q55" s="3">
-        <f>C55-N55</f>
+      <c r="Q55">
+        <f t="shared" si="4"/>
         <v>19.240000000000009</v>
       </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S55" s="3">
+        <v>7</v>
+      </c>
+      <c r="T55" s="4">
+        <v>1054.5999999999999</v>
+      </c>
+      <c r="U55">
+        <f t="shared" si="2"/>
+        <v>-3</v>
+      </c>
+      <c r="V55">
+        <f t="shared" si="3"/>
+        <v>110.96000000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>48</v>
       </c>
@@ -3341,12 +4196,26 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q56" s="2">
-        <f>C56-N56</f>
+      <c r="Q56" s="1">
+        <f t="shared" si="4"/>
         <v>-34.580000000000155</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S56" s="3">
+        <v>6</v>
+      </c>
+      <c r="T56" s="4">
+        <v>966.08</v>
+      </c>
+      <c r="U56">
+        <f t="shared" si="2"/>
+        <v>-1</v>
+      </c>
+      <c r="V56">
+        <f t="shared" si="3"/>
+        <v>60.479999999999905</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>49</v>
       </c>
@@ -3387,9 +4256,23 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="Q57" s="2">
-        <f>C57-N57</f>
+      <c r="Q57" s="1">
+        <f t="shared" si="4"/>
         <v>-17.960000000000036</v>
+      </c>
+      <c r="S57" s="3">
+        <v>4</v>
+      </c>
+      <c r="T57" s="4">
+        <v>778.93</v>
+      </c>
+      <c r="U57">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="V57">
+        <f t="shared" si="3"/>
+        <v>31.25</v>
       </c>
     </row>
   </sheetData>
@@ -3399,4 +4282,500 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4F48B62-931E-4837-A8D9-109649C3215B}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5">
+        <v>1650.8</v>
+      </c>
+      <c r="B1" s="7">
+        <v>1650.8</v>
+      </c>
+      <c r="C1" s="7">
+        <v>1669.81</v>
+      </c>
+      <c r="D1" s="7">
+        <v>1643.18</v>
+      </c>
+      <c r="E1" s="7">
+        <v>1648.08</v>
+      </c>
+      <c r="F1" s="7">
+        <v>1646.6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>1486.12</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1486.86</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1499</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1476.11</v>
+      </c>
+      <c r="E2" s="8">
+        <v>1486.12</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1472.81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>1292.68</v>
+      </c>
+      <c r="B3" s="8">
+        <v>1292.68</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1240.08</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1245.8599999999999</v>
+      </c>
+      <c r="E3" s="8">
+        <v>1299.99</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1257.6500000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>1007.31</v>
+      </c>
+      <c r="B4" s="8">
+        <v>1007.31</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1626.47</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1026.9100000000001</v>
+      </c>
+      <c r="E4" s="9">
+        <v>996.27</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1017.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>1377.11</v>
+      </c>
+      <c r="B5" s="8">
+        <v>1377.11</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1391.59</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1361.39</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1377.11</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1393.89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>1252.03</v>
+      </c>
+      <c r="B6" s="9">
+        <v>1252.03</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1261.06</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1264.5</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1262.8</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1252.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>1104.6600000000001</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1104.6600000000001</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1127.8399999999999</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1108.1099999999999</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1081.17</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1093.8399999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>960.88</v>
+      </c>
+      <c r="B8" s="8">
+        <v>960.88</v>
+      </c>
+      <c r="C8" s="8">
+        <v>990.62</v>
+      </c>
+      <c r="D8" s="8">
+        <v>994.68</v>
+      </c>
+      <c r="E8" s="8">
+        <v>985.76</v>
+      </c>
+      <c r="F8" s="8">
+        <v>958.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>1194.73</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1194.73</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1197.33</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1168.9100000000001</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1210.73</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1154.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>1118.8399999999999</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1118.8399999999999</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1125.04</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1108.22</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1101.49</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1135.0999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>1096.72</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1096.73</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1090.52</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1080.8399999999999</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1064.67</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1071.6400000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>982.14</v>
+      </c>
+      <c r="B12" s="8">
+        <v>982.14</v>
+      </c>
+      <c r="C12" s="8">
+        <v>982.91</v>
+      </c>
+      <c r="D12" s="8">
+        <v>992.22</v>
+      </c>
+      <c r="E12" s="9">
+        <v>974.95</v>
+      </c>
+      <c r="F12" s="8">
+        <v>993.68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>1252.3699999999999</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1252.3699999999999</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1260.58</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1197.0899999999999</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1252.3699999999999</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1189.74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>1191.7</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1191.7</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1097.58</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1092.22</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1225.02</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1147.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>939.5</v>
+      </c>
+      <c r="B15" s="8">
+        <v>939.5</v>
+      </c>
+      <c r="C15" s="8">
+        <v>962.4</v>
+      </c>
+      <c r="D15" s="8">
+        <v>983.06</v>
+      </c>
+      <c r="E15" s="8">
+        <v>962.25</v>
+      </c>
+      <c r="F15" s="8">
+        <v>910.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>825.52</v>
+      </c>
+      <c r="B16" s="9">
+        <v>731.3</v>
+      </c>
+      <c r="C16" s="8">
+        <v>807.29</v>
+      </c>
+      <c r="D16" s="8">
+        <v>845.3</v>
+      </c>
+      <c r="E16" s="8">
+        <v>766.13</v>
+      </c>
+      <c r="F16" s="8">
+        <v>774.85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>994.43</v>
+      </c>
+      <c r="B17" s="9">
+        <v>965.1</v>
+      </c>
+      <c r="C17" s="8">
+        <v>1036.02</v>
+      </c>
+      <c r="D17" s="8">
+        <v>999.54</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1027.79</v>
+      </c>
+      <c r="F17" s="8">
+        <v>998.23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>906.14</v>
+      </c>
+      <c r="B18" s="9">
+        <v>887.6</v>
+      </c>
+      <c r="C18" s="8">
+        <v>941.09</v>
+      </c>
+      <c r="D18" s="8">
+        <v>955.94</v>
+      </c>
+      <c r="E18" s="8">
+        <v>939.46</v>
+      </c>
+      <c r="F18" s="8">
+        <v>950.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>890.61</v>
+      </c>
+      <c r="B19" s="9">
+        <v>807</v>
+      </c>
+      <c r="C19" s="8">
+        <v>892.61</v>
+      </c>
+      <c r="D19" s="8">
+        <v>903.59</v>
+      </c>
+      <c r="E19" s="8">
+        <v>872.4</v>
+      </c>
+      <c r="F19" s="8">
+        <v>851.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>726.82</v>
+      </c>
+      <c r="B20" s="9">
+        <v>703.4</v>
+      </c>
+      <c r="C20" s="8">
+        <v>805.5</v>
+      </c>
+      <c r="D20" s="8">
+        <v>769.96</v>
+      </c>
+      <c r="E20" s="8">
+        <v>740.36</v>
+      </c>
+      <c r="F20" s="8">
+        <v>737.56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>909.16</v>
+      </c>
+      <c r="B21" s="8">
+        <v>909.16</v>
+      </c>
+      <c r="C21" s="8">
+        <v>938.48</v>
+      </c>
+      <c r="D21" s="8">
+        <v>935.57</v>
+      </c>
+      <c r="E21" s="8">
+        <v>943.72</v>
+      </c>
+      <c r="F21" s="8">
+        <v>904.34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>939.37</v>
+      </c>
+      <c r="B22" s="8">
+        <v>944.7</v>
+      </c>
+      <c r="C22" s="8">
+        <v>981.4</v>
+      </c>
+      <c r="D22" s="8">
+        <v>988.34</v>
+      </c>
+      <c r="E22" s="8">
+        <v>965.88</v>
+      </c>
+      <c r="F22" s="8">
+        <v>964.67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>885.71</v>
+      </c>
+      <c r="B23" s="9">
+        <v>754.6</v>
+      </c>
+      <c r="C23" s="8">
+        <v>854.82</v>
+      </c>
+      <c r="D23" s="8">
+        <v>867.95</v>
+      </c>
+      <c r="E23" s="8">
+        <v>828.9</v>
+      </c>
+      <c r="F23" s="8">
+        <v>773.45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f>AVERAGE(A1:A23)</f>
+        <v>1086.3195652173911</v>
+      </c>
+      <c r="B24">
+        <f t="shared" ref="B24:F24" si="0">AVERAGE(B1:B23)</f>
+        <v>1070.0521739130431</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>1120.8713043478263</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>1087.3691304347826</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>1087.5400000000002</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>1071.8156521739129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>